--- a/#American_anonymized.xlsx
+++ b/#American_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -616,7 +616,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -868,7 +868,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -936,7 +936,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1248,7 +1248,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_00132</t>
+          <t>user_00134</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1392,12 +1392,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1497,12 +1497,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1529,12 +1529,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1562,12 +1562,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1658,12 +1658,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1722,12 +1722,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1754,12 +1754,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1786,12 +1786,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1818,12 +1818,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1850,12 +1850,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1884,12 +1884,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1917,12 +1917,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2016,12 +2016,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>user_00292</t>
+          <t>user_00299</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>user_02274</t>
+          <t>user_02305</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2081,12 +2081,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2126,12 +2126,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2173,12 +2173,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2220,12 +2220,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2266,12 +2266,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2310,12 +2310,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2400,12 +2400,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2439,12 +2439,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2516,12 +2516,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2548,12 +2548,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2647,12 +2647,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2712,12 +2712,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2747,12 +2747,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2814,12 +2814,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2846,12 +2846,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3075,12 +3075,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3108,12 +3108,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>user_01762</t>
+          <t>user_01783</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>user_02755</t>
+          <t>user_02817</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3124,7 +3124,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3146,12 +3146,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3186,12 +3186,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3225,12 +3225,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3290,12 +3290,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3324,12 +3324,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3357,12 +3357,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3389,12 +3389,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3421,12 +3421,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3453,12 +3453,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3485,12 +3485,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3517,12 +3517,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3549,12 +3549,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3618,12 +3618,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3650,12 +3650,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3682,12 +3682,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3746,12 +3746,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3778,12 +3778,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3810,12 +3810,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>user_01376</t>
+          <t>user_01396</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>user_02576</t>
+          <t>user_02629</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3842,12 +3842,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3858,7 +3858,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3881,12 +3881,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3981,12 +3981,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4018,12 +4018,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4054,12 +4054,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4088,12 +4088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4121,12 +4121,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4154,12 +4154,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4186,12 +4186,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4218,12 +4218,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4250,12 +4250,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4314,12 +4314,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4346,12 +4346,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4378,12 +4378,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4410,12 +4410,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4442,12 +4442,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4474,12 +4474,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>user_00945</t>
+          <t>user_00958</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>user_00946</t>
+          <t>user_00959</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4524,7 +4524,7 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4547,12 +4547,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4580,12 +4580,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4613,12 +4613,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4646,12 +4646,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4712,12 +4712,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,12 +4745,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4778,12 +4778,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4844,12 +4844,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4877,12 +4877,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4910,12 +4910,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4944,12 +4944,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4977,12 +4977,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5010,12 +5010,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5084,12 +5084,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5150,12 +5150,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>user_01955</t>
+          <t>user_01978</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>user_01561</t>
+          <t>user_01582</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5183,12 +5183,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>user_00174</t>
+          <t>user_00178</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>user_00174</t>
+          <t>user_00178</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5199,7 +5199,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -5221,12 +5221,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>user_00658</t>
+          <t>user_00669</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>user_00659</t>
+          <t>user_00670</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5237,7 +5237,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -5261,12 +5261,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>user_00424</t>
+          <t>user_00432</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>user_00425</t>
+          <t>user_00433</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5277,7 +5277,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -5299,12 +5299,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5315,7 +5315,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5341,12 +5341,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5373,12 +5373,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5409,12 +5409,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5441,12 +5441,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5474,12 +5474,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5506,12 +5506,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5538,12 +5538,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5634,12 +5634,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5666,12 +5666,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5698,12 +5698,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5730,12 +5730,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5797,12 +5797,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5863,12 +5863,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5895,12 +5895,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>user_00917</t>
+          <t>user_00930</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>user_02429</t>
+          <t>user_02473</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5992,12 +5992,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6008,7 +6008,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -6033,12 +6033,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6074,12 +6074,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6114,12 +6114,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6150,12 +6150,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6186,12 +6186,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6222,12 +6222,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6258,12 +6258,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6290,12 +6290,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6323,12 +6323,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6356,12 +6356,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6389,12 +6389,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6422,12 +6422,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6455,12 +6455,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6520,12 +6520,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6553,12 +6553,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6585,12 +6585,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6683,12 +6683,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>user_01560</t>
+          <t>user_01581</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>user_02624</t>
+          <t>user_02680</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6716,12 +6716,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -6759,12 +6759,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6802,12 +6802,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6836,12 +6836,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6868,12 +6868,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6901,12 +6901,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6935,12 +6935,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6967,12 +6967,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7000,12 +7000,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7032,12 +7032,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7067,12 +7067,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7100,12 +7100,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7134,12 +7134,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7166,12 +7166,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7199,12 +7199,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7231,12 +7231,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7263,12 +7263,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7295,12 +7295,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7327,12 +7327,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7361,12 +7361,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7395,12 +7395,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7428,12 +7428,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>user_01679</t>
+          <t>user_01700</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>user_01681</t>
+          <t>user_01702</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7444,7 +7444,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -7469,12 +7469,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7485,7 +7485,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -7508,12 +7508,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7540,12 +7540,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7572,12 +7572,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7604,12 +7604,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7636,12 +7636,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7669,12 +7669,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7701,12 +7701,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7733,12 +7733,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7766,12 +7766,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7799,12 +7799,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7831,12 +7831,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7863,12 +7863,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7895,12 +7895,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7927,12 +7927,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7959,12 +7959,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7992,12 +7992,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8024,12 +8024,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8056,12 +8056,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8090,12 +8090,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8122,12 +8122,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>user_01408</t>
+          <t>user_01428</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>user_01407</t>
+          <t>user_01427</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8154,12 +8154,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8170,7 +8170,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -8194,12 +8194,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8226,12 +8226,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8258,12 +8258,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8291,12 +8291,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8324,12 +8324,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8357,12 +8357,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8389,12 +8389,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8421,12 +8421,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8454,12 +8454,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8487,12 +8487,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8519,12 +8519,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8551,12 +8551,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8584,12 +8584,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8616,12 +8616,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8652,12 +8652,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8685,12 +8685,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8718,12 +8718,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8750,12 +8750,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8783,12 +8783,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8818,12 +8818,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>user_01843</t>
+          <t>user_01864</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>user_01844</t>
+          <t>user_01865</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8850,12 +8850,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8866,7 +8866,7 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -8888,12 +8888,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8920,12 +8920,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8952,12 +8952,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8984,12 +8984,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9016,12 +9016,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9050,12 +9050,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9086,12 +9086,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9118,12 +9118,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9150,12 +9150,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9186,12 +9186,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9218,12 +9218,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9250,12 +9250,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9283,12 +9283,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9316,12 +9316,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9348,12 +9348,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9449,12 +9449,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9481,12 +9481,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9513,12 +9513,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>user_01523</t>
+          <t>user_01544</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>user_01524</t>
+          <t>user_01545</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9545,12 +9545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9561,7 +9561,7 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -9583,12 +9583,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9615,12 +9615,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9648,12 +9648,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9680,12 +9680,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9712,12 +9712,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9744,12 +9744,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9776,12 +9776,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9808,12 +9808,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9840,12 +9840,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9872,12 +9872,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9904,12 +9904,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9936,12 +9936,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9968,12 +9968,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10000,12 +10000,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10032,12 +10032,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10064,12 +10064,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10096,12 +10096,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10128,12 +10128,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10160,12 +10160,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10192,12 +10192,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10208,7 +10208,7 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -10233,12 +10233,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10265,12 +10265,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10297,12 +10297,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10330,12 +10330,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10362,12 +10362,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10394,12 +10394,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10426,12 +10426,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10460,12 +10460,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10493,12 +10493,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10525,12 +10525,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10557,12 +10557,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10589,12 +10589,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10621,12 +10621,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10653,12 +10653,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10685,12 +10685,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>user_01757</t>
+          <t>user_01778</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>user_01758</t>
+          <t>user_01779</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10719,12 +10719,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10735,7 +10735,7 @@
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -10761,12 +10761,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10777,7 +10777,7 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -10803,12 +10803,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10819,7 +10819,7 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -10845,12 +10845,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10861,7 +10861,7 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -10887,12 +10887,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -10903,7 +10903,7 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -10929,12 +10929,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10945,7 +10945,7 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -10971,12 +10971,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10987,7 +10987,7 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -11013,12 +11013,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11045,12 +11045,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11078,12 +11078,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11110,12 +11110,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11142,12 +11142,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11174,12 +11174,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11206,12 +11206,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11238,12 +11238,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11270,12 +11270,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11302,12 +11302,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -11334,12 +11334,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11366,12 +11366,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -11398,12 +11398,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -11430,12 +11430,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11462,12 +11462,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11494,12 +11494,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -11526,12 +11526,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -11558,12 +11558,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -11590,12 +11590,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>user_01650</t>
+          <t>user_01671</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -11622,12 +11622,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>user_00098</t>
+          <t>user_00100</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>user_02192</t>
+          <t>user_02217</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -11638,7 +11638,7 @@
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -11662,12 +11662,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -11678,7 +11678,7 @@
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -11701,12 +11701,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -11744,12 +11744,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -11778,12 +11778,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -11810,12 +11810,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -11843,12 +11843,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11877,12 +11877,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11909,12 +11909,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -11942,12 +11942,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -11974,12 +11974,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -12009,12 +12009,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -12042,12 +12042,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -12076,12 +12076,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -12108,12 +12108,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -12141,12 +12141,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -12173,12 +12173,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -12205,12 +12205,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -12237,12 +12237,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -12269,12 +12269,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -12303,12 +12303,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -12337,12 +12337,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>user_01558</t>
+          <t>user_01579</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>user_01559</t>
+          <t>user_01580</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -12370,12 +12370,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -12386,7 +12386,7 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -12414,12 +12414,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -12446,12 +12446,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -12483,12 +12483,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -12519,12 +12519,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -12557,12 +12557,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -12590,12 +12590,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -12623,12 +12623,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -12659,12 +12659,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -12693,12 +12693,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -12726,12 +12726,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -12760,12 +12760,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -12794,12 +12794,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -12828,12 +12828,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -12864,12 +12864,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -12898,12 +12898,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -12933,12 +12933,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -12970,12 +12970,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -13006,12 +13006,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -13039,12 +13039,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -13073,12 +13073,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -13089,7 +13089,7 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -13113,12 +13113,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -13145,12 +13145,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -13178,12 +13178,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -13210,12 +13210,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -13243,12 +13243,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -13275,12 +13275,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -13308,12 +13308,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -13340,12 +13340,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -13373,12 +13373,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -13405,12 +13405,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -13438,12 +13438,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -13470,12 +13470,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -13503,12 +13503,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -13535,12 +13535,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -13568,12 +13568,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -13600,12 +13600,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -13633,12 +13633,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -13665,12 +13665,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>user_01725</t>
+          <t>user_01746</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>user_01726</t>
+          <t>user_01747</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -13698,12 +13698,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -13714,7 +13714,7 @@
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F391" t="n">
@@ -13736,12 +13736,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -13768,12 +13768,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -13806,12 +13806,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -13838,12 +13838,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -13870,12 +13870,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -13908,12 +13908,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -13942,12 +13942,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -13975,12 +13975,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -14007,12 +14007,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -14039,12 +14039,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -14071,12 +14071,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -14103,12 +14103,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -14135,12 +14135,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -14169,12 +14169,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -14201,12 +14201,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -14233,12 +14233,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -14265,12 +14265,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -14302,12 +14302,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -14340,12 +14340,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>user_00198</t>
+          <t>user_00202</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>user_00199</t>
+          <t>user_00203</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -14376,12 +14376,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -14392,7 +14392,7 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>user_02795</t>
+          <t>user_02859</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -14417,12 +14417,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -14450,12 +14450,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -14483,12 +14483,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -14516,12 +14516,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -14548,12 +14548,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -14580,12 +14580,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -14612,12 +14612,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -14645,12 +14645,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -14677,12 +14677,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -14709,12 +14709,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -14741,12 +14741,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -14773,12 +14773,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -14805,12 +14805,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -14873,12 +14873,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -14905,12 +14905,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -14937,12 +14937,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -14970,12 +14970,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -15002,12 +15002,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -15035,12 +15035,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>user_02968</t>
+          <t>user_03048</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>user_02437</t>
+          <t>user_02481</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -15068,12 +15068,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>user_01642</t>
+          <t>user_01663</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -15114,12 +15114,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>user_01642</t>
+          <t>user_01663</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>user_01390</t>
+          <t>user_01410</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -15160,12 +15160,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -15202,12 +15202,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -15250,12 +15250,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -15295,12 +15295,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -15337,12 +15337,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -15383,12 +15383,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -15415,12 +15415,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15452,12 +15452,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -15488,12 +15488,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -15526,12 +15526,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -15559,12 +15559,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -15592,12 +15592,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -15628,12 +15628,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -15662,12 +15662,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -15695,12 +15695,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -15729,12 +15729,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -15763,12 +15763,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -15797,12 +15797,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -15833,12 +15833,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -15867,12 +15867,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -15902,12 +15902,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -15939,12 +15939,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -15975,12 +15975,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -16008,12 +16008,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>user_01989</t>
+          <t>user_02013</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -16042,12 +16042,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -16058,7 +16058,7 @@
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -16083,12 +16083,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -16120,12 +16120,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16156,12 +16156,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -16192,12 +16192,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -16225,12 +16225,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -16259,12 +16259,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -16295,12 +16295,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -16331,12 +16331,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -16365,12 +16365,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16400,12 +16400,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -16434,12 +16434,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -16467,12 +16467,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16501,12 +16501,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16535,12 +16535,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16568,12 +16568,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -16602,12 +16602,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -16635,12 +16635,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -16669,12 +16669,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16703,12 +16703,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16736,12 +16736,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16773,12 +16773,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>user_00111</t>
+          <t>user_00113</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>user_00082</t>
+          <t>user_00083</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -16789,7 +16789,7 @@
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -16812,12 +16812,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -16828,7 +16828,7 @@
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -16850,12 +16850,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -16883,12 +16883,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -16915,12 +16915,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -16947,12 +16947,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -16985,12 +16985,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -17018,12 +17018,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -17051,12 +17051,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -17084,12 +17084,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -17116,12 +17116,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -17150,12 +17150,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -17182,12 +17182,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -17216,12 +17216,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -17248,12 +17248,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -17281,12 +17281,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -17313,12 +17313,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -17349,12 +17349,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -17382,12 +17382,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -17415,12 +17415,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -17447,12 +17447,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -17479,12 +17479,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>user_01287</t>
+          <t>user_01307</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>user_01288</t>
+          <t>user_01308</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -17512,12 +17512,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -17528,7 +17528,7 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -17550,12 +17550,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -17582,12 +17582,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -17614,12 +17614,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -17648,12 +17648,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -17682,12 +17682,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -17714,12 +17714,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -17746,12 +17746,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -17778,12 +17778,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -17812,12 +17812,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -17844,12 +17844,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -17876,12 +17876,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -17908,12 +17908,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -17940,12 +17940,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -17972,12 +17972,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18004,12 +18004,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18036,12 +18036,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18069,12 +18069,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18101,12 +18101,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18134,12 +18134,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>user_00070</t>
+          <t>user_00071</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>user_01992</t>
+          <t>user_02016</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18166,12 +18166,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -18182,7 +18182,7 @@
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -18206,12 +18206,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -18240,12 +18240,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -18275,12 +18275,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -18307,12 +18307,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -18339,12 +18339,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -18372,12 +18372,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -18406,12 +18406,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -18439,12 +18439,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -18471,12 +18471,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -18505,12 +18505,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -18539,12 +18539,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -18571,12 +18571,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -18603,12 +18603,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -18635,12 +18635,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -18668,12 +18668,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -18701,12 +18701,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -18734,12 +18734,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -18767,12 +18767,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>user_00189</t>
+          <t>user_00193</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>user_00190</t>
+          <t>user_00194</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -18815,7 +18815,7 @@
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>user_01990</t>
+          <t>user_02014</t>
         </is>
       </c>
       <c r="F540" t="n">
@@ -19472,12 +19472,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -19510,12 +19510,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -19551,12 +19551,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -19591,12 +19591,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -19631,12 +19631,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -19672,12 +19672,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -19714,12 +19714,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -19759,12 +19759,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -19796,12 +19796,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -19832,12 +19832,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -19868,12 +19868,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -19901,12 +19901,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -19935,12 +19935,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -19971,12 +19971,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -20007,12 +20007,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -20041,12 +20041,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -20076,12 +20076,12 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -20110,12 +20110,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -20143,12 +20143,12 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -20177,12 +20177,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -20211,12 +20211,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -20244,12 +20244,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -20278,12 +20278,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -20311,12 +20311,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -20345,12 +20345,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -20379,12 +20379,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -20412,12 +20412,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>user_01382</t>
+          <t>user_01402</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -20449,12 +20449,12 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -20465,7 +20465,7 @@
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -20487,12 +20487,12 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -20519,12 +20519,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -20552,12 +20552,12 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -20585,12 +20585,12 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -20620,12 +20620,12 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -20652,12 +20652,12 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -20684,12 +20684,12 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -20717,12 +20717,12 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -20749,12 +20749,12 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -20783,12 +20783,12 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -20816,12 +20816,12 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -20848,12 +20848,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -20880,12 +20880,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -20912,12 +20912,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -20944,12 +20944,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -20976,12 +20976,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>user_02779</t>
+          <t>user_02842</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>user_02780</t>
+          <t>user_02843</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -21009,12 +21009,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>user_00815</t>
+          <t>user_00828</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>user_02388</t>
+          <t>user_02430</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -21025,7 +21025,7 @@
       <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -21047,12 +21047,12 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -21063,7 +21063,7 @@
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -21087,12 +21087,12 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -21119,12 +21119,12 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -21151,12 +21151,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -21186,12 +21186,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -21218,12 +21218,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -21256,12 +21256,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -21290,12 +21290,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -21328,12 +21328,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -21362,12 +21362,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -21396,12 +21396,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -21434,12 +21434,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -21471,12 +21471,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -21506,12 +21506,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -21539,12 +21539,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>user_00901</t>
+          <t>user_00914</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>user_00902</t>
+          <t>user_00915</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -21574,12 +21574,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -21590,7 +21590,7 @@
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F620" t="n">
@@ -21613,12 +21613,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -21650,12 +21650,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -21686,12 +21686,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -21719,12 +21719,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -21751,12 +21751,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -21784,12 +21784,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -21817,12 +21817,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -21854,12 +21854,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -21886,12 +21886,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -21919,12 +21919,12 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -21953,12 +21953,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -21985,12 +21985,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -22017,12 +22017,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -22050,12 +22050,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -22084,12 +22084,12 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -22117,12 +22117,12 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -22150,12 +22150,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -22183,12 +22183,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -22223,12 +22223,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -22260,12 +22260,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>user_01368</t>
+          <t>user_01388</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>user_01239</t>
+          <t>user_01259</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -22308,7 +22308,7 @@
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F641" t="n">
@@ -22330,12 +22330,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>user_00510</t>
+          <t>user_00518</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>user_00809</t>
+          <t>user_00822</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -22346,7 +22346,7 @@
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
-          <t>user_01383</t>
+          <t>user_01403</t>
         </is>
       </c>
       <c r="F642" t="n">

--- a/#American_anonymized.xlsx
+++ b/#American_anonymized.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
